--- a/缓存数据/pca.xlsx
+++ b/缓存数据/pca.xlsx
@@ -548,7 +548,7 @@
         <v>43798</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,28 +559,28 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>48.01</v>
+        <v>59.74</v>
       </c>
       <c r="L2" t="n">
-        <v>59.74</v>
+        <v>35.03</v>
       </c>
       <c r="M2" t="n">
-        <v>35.03</v>
+        <v>67.17</v>
       </c>
       <c r="N2" t="n">
-        <v>67.17</v>
+        <v>36.65</v>
       </c>
       <c r="O2" t="n">
-        <v>36.65</v>
+        <v>43.85</v>
       </c>
       <c r="P2" t="n">
-        <v>43.85</v>
+        <v>34</v>
       </c>
       <c r="Q2" t="n">
-        <v>34</v>
+        <v>64.48</v>
       </c>
       <c r="R2" t="n">
-        <v>64.48</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="3">
@@ -612,7 +612,7 @@
         <v>42604</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -623,28 +623,28 @@
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>36.27</v>
+        <v>39.07</v>
       </c>
       <c r="L3" t="n">
-        <v>39.07</v>
+        <v>34.52</v>
       </c>
       <c r="M3" t="n">
-        <v>34.52</v>
+        <v>50.65</v>
       </c>
       <c r="N3" t="n">
-        <v>50.65</v>
+        <v>26.25</v>
       </c>
       <c r="O3" t="n">
-        <v>26.25</v>
+        <v>30.68</v>
       </c>
       <c r="P3" t="n">
-        <v>30.68</v>
+        <v>33.37</v>
       </c>
       <c r="Q3" t="n">
-        <v>33.37</v>
+        <v>41.12</v>
       </c>
       <c r="R3" t="n">
-        <v>41.12</v>
+        <v>30.48</v>
       </c>
     </row>
     <row r="4">
@@ -676,7 +676,7 @@
         <v>41776</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.57</v>
+        <v>1.77</v>
       </c>
       <c r="L4" t="n">
-        <v>1.77</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>8.970000000000001</v>
+        <v>1.21</v>
       </c>
       <c r="N4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>6.39</v>
       </c>
       <c r="P4" t="n">
-        <v>6.39</v>
+        <v>5.43</v>
       </c>
       <c r="Q4" t="n">
-        <v>5.43</v>
+        <v>6.22</v>
       </c>
       <c r="R4" t="n">
-        <v>6.22</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="5">
@@ -740,7 +740,7 @@
         <v>43447</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -751,28 +751,28 @@
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>264.03</v>
+        <v>211.64</v>
       </c>
       <c r="L5" t="n">
-        <v>211.64</v>
+        <v>251.32</v>
       </c>
       <c r="M5" t="n">
-        <v>251.32</v>
+        <v>201.24</v>
       </c>
       <c r="N5" t="n">
-        <v>201.24</v>
+        <v>200.2</v>
       </c>
       <c r="O5" t="n">
-        <v>200.2</v>
+        <v>203.34</v>
       </c>
       <c r="P5" t="n">
-        <v>203.34</v>
+        <v>201.66</v>
       </c>
       <c r="Q5" t="n">
-        <v>201.66</v>
+        <v>204.2</v>
       </c>
       <c r="R5" t="n">
-        <v>204.2</v>
+        <v>222.17</v>
       </c>
     </row>
     <row r="6">
@@ -804,7 +804,7 @@
         <v>44357</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -815,28 +815,28 @@
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>58.24</v>
+        <v>74.77</v>
       </c>
       <c r="L6" t="n">
-        <v>74.77</v>
+        <v>103.41</v>
       </c>
       <c r="M6" t="n">
-        <v>103.41</v>
+        <v>57.98</v>
       </c>
       <c r="N6" t="n">
-        <v>57.98</v>
+        <v>61.72</v>
       </c>
       <c r="O6" t="n">
-        <v>61.72</v>
+        <v>84.66</v>
       </c>
       <c r="P6" t="n">
-        <v>84.66</v>
+        <v>59.08</v>
       </c>
       <c r="Q6" t="n">
-        <v>59.08</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="R6" t="n">
-        <v>77.65000000000001</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="7">
@@ -868,7 +868,7 @@
         <v>43372</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -879,28 +879,28 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>110.65</v>
+        <v>93.34</v>
       </c>
       <c r="L7" t="n">
-        <v>93.34</v>
+        <v>77.89</v>
       </c>
       <c r="M7" t="n">
-        <v>77.89</v>
+        <v>103.31</v>
       </c>
       <c r="N7" t="n">
-        <v>103.31</v>
+        <v>98.94</v>
       </c>
       <c r="O7" t="n">
-        <v>98.94</v>
+        <v>102.68</v>
       </c>
       <c r="P7" t="n">
-        <v>102.68</v>
+        <v>111.44</v>
       </c>
       <c r="Q7" t="n">
-        <v>111.44</v>
+        <v>106.74</v>
       </c>
       <c r="R7" t="n">
-        <v>106.74</v>
+        <v>26.85</v>
       </c>
     </row>
     <row r="8">
@@ -943,16 +943,16 @@
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>119.06</v>
+        <v>63.56</v>
       </c>
       <c r="L8" t="n">
-        <v>63.56</v>
+        <v>166.76</v>
       </c>
       <c r="M8" t="n">
-        <v>166.76</v>
+        <v>32.4</v>
       </c>
       <c r="N8" t="n">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -972,20 +972,20 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>37845140</v>
+        <v>33955470</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>平和华宇</t>
+          <t>鑫通源电子</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>福建平和华宇机械有限公司</t>
+          <t>泉州市鑫通源电子科技有限公司</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>429427348</v>
+        <v>429351055</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -993,42 +993,42 @@
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>44739</v>
+        <v>44496</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>漳州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>11.67</v>
+        <v>5.67</v>
       </c>
       <c r="L9" t="n">
-        <v>4.34</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>6.97</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>5.91</v>
+        <v>0.1</v>
       </c>
       <c r="P9" t="n">
-        <v>8.75</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>16.92</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="10">
@@ -1036,20 +1036,20 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>33955470</v>
+        <v>37845140</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>鑫通源电子</t>
+          <t>平和华宇</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>泉州市鑫通源电子科技有限公司</t>
+          <t>福建平和华宇机械有限公司</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>429351055</v>
+        <v>429427348</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1057,39 +1057,39 @@
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>44496</v>
+        <v>44739</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45152</v>
+        <v>45154</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>漳州市</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>13.34</v>
+        <v>4.34</v>
       </c>
       <c r="L10" t="n">
-        <v>5.67</v>
+        <v>6.97</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.91</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>8.75</v>
       </c>
       <c r="P10" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>16.92</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1124,7 +1124,7 @@
         <v>43720</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>45154</v>
+        <v>45155</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1135,28 +1135,28 @@
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>40.5</v>
+        <v>16.77</v>
       </c>
       <c r="L11" t="n">
-        <v>16.77</v>
+        <v>93.40000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>93.40000000000001</v>
+        <v>48.04</v>
       </c>
       <c r="N11" t="n">
-        <v>48.04</v>
+        <v>33.23</v>
       </c>
       <c r="O11" t="n">
-        <v>33.23</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="P11" t="n">
-        <v>79.29000000000001</v>
+        <v>31.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>31.07</v>
+        <v>42.48</v>
       </c>
       <c r="R11" t="n">
-        <v>42.48</v>
+        <v>41.57</v>
       </c>
     </row>
   </sheetData>

--- a/缓存数据/pca.xlsx
+++ b/缓存数据/pca.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="yyyy-mm-dd h:mm:ss" numFmtId="164"/>
-    <numFmt formatCode="YYYY-MM-DD HH:MM:SS" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -56,19 +56,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:R81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -524,31 +524,31 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>29470497</v>
+        <v>31215107</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>厦门安世通</t>
+          <t>网宝网络</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>厦门安世通国际快递物流有限公司</t>
+          <t>厦门网宝网络服务有限公司</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>427747649</v>
+        <v>428974694</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>老户新开</t>
+          <t>首次上线新客户</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>43798</v>
+        <v>44082</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>45155</v>
+        <v>45191</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -559,28 +559,28 @@
         <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>59.74</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>35.03</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>67.17</v>
+        <v>509.5</v>
       </c>
       <c r="N2" t="n">
-        <v>36.65</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>43.85</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>64.48</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>75.52</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -588,20 +588,20 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21851164</v>
+        <v>35400095</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宏腾包装</t>
+          <t>漳州铭清工贸</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>福建宏腾包装有限公司</t>
+          <t>漳州市铭清工贸有限公司</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>428394407</v>
+        <v>429382914</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -609,42 +609,42 @@
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>42604</v>
+        <v>44496</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>45155</v>
+        <v>45192</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>漳州市</t>
         </is>
       </c>
       <c r="J3" t="n">
         <v>1</v>
       </c>
       <c r="K3" t="n">
-        <v>39.07</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>34.52</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>50.65</v>
+        <v>0</v>
       </c>
       <c r="N3" t="n">
-        <v>26.25</v>
+        <v>506.84</v>
       </c>
       <c r="O3" t="n">
-        <v>30.68</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>33.37</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>41.12</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>30.48</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -652,20 +652,20 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>7310846</v>
+        <v>33779287</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>厦门安政</t>
+          <t>仟禾源</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>厦门安政交通设施工程有限公司</t>
+          <t>仟禾源知识产权（厦门）有限公司</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>199941619</v>
+        <v>429343570</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>41776</v>
+        <v>44417</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>45155</v>
+        <v>45189</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -687,28 +687,28 @@
         <v>1</v>
       </c>
       <c r="K4" t="n">
-        <v>1.77</v>
+        <v>241.18</v>
       </c>
       <c r="L4" t="n">
-        <v>8.970000000000001</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>6.39</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>5.43</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>6.22</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>7.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -716,63 +716,63 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26910059</v>
+        <v>29470497</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>炎顺建材泉州</t>
+          <t>厦门安世通</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>随州市炎顺建材有限公司泉州分公司</t>
+          <t>厦门安世通国际快递物流有限公司</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>428845812</v>
+        <v>427747649</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>首次上线新客户</t>
+          <t>老户新开</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>43447</v>
+        <v>43798</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>45155</v>
+        <v>45196</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="J5" t="n">
         <v>1</v>
       </c>
       <c r="K5" t="n">
-        <v>211.64</v>
+        <v>5.57</v>
       </c>
       <c r="L5" t="n">
-        <v>251.32</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>201.24</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>200.2</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>203.34</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>201.66</v>
+        <v>11.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>204.2</v>
+        <v>48.63</v>
       </c>
       <c r="R5" t="n">
-        <v>222.17</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="6">
@@ -780,63 +780,63 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33404220</v>
+        <v>24902767</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>晋江星韵</t>
+          <t>厦门速达</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>晋江市梅岭星韵办公用品商行</t>
+          <t>厦门速达软件有限公司</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>429330423</v>
+        <v>51292099</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>首次上线新客户</t>
+          <t>老户新开</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>44357</v>
+        <v>43092</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>45155</v>
+        <v>45194</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="J6" t="n">
         <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>74.77</v>
+        <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>103.41</v>
+        <v>497.7</v>
       </c>
       <c r="M6" t="n">
-        <v>57.98</v>
+        <v>4.76</v>
       </c>
       <c r="N6" t="n">
-        <v>61.72</v>
+        <v>6.41</v>
       </c>
       <c r="O6" t="n">
-        <v>84.66</v>
+        <v>2.48</v>
       </c>
       <c r="P6" t="n">
-        <v>59.08</v>
+        <v>29.58</v>
       </c>
       <c r="Q6" t="n">
-        <v>77.65000000000001</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>103.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -844,20 +844,20 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26463585</v>
+        <v>21851164</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>璐霖回收</t>
+          <t>宏腾包装</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>南安市丰州璐霖废品回收站</t>
+          <t>福建宏腾包装有限公司</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>428843680</v>
+        <v>428394407</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>43372</v>
+        <v>42604</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>45155</v>
+        <v>45196</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -879,28 +879,28 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>93.34</v>
+        <v>26.4</v>
       </c>
       <c r="L7" t="n">
-        <v>77.89</v>
+        <v>24.17</v>
       </c>
       <c r="M7" t="n">
-        <v>103.31</v>
+        <v>18.75</v>
       </c>
       <c r="N7" t="n">
-        <v>98.94</v>
+        <v>38.16</v>
       </c>
       <c r="O7" t="n">
-        <v>102.68</v>
+        <v>25.41</v>
       </c>
       <c r="P7" t="n">
-        <v>111.44</v>
+        <v>46.68</v>
       </c>
       <c r="Q7" t="n">
-        <v>106.74</v>
+        <v>26.53</v>
       </c>
       <c r="R7" t="n">
-        <v>26.85</v>
+        <v>24.22</v>
       </c>
     </row>
     <row r="8">
@@ -908,20 +908,20 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>30306749</v>
+        <v>29319432</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>唐志峰律师</t>
+          <t>启砾文化</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>唐志峰</t>
+          <t>厦门启砾文化传媒有限公司</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>429142003</v>
+        <v>429053001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -929,27 +929,27 @@
         </is>
       </c>
       <c r="G8" s="2" t="n">
-        <v>43937</v>
+        <v>43781</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>45150</v>
+        <v>45190</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="J8" t="n">
         <v>1</v>
       </c>
       <c r="K8" t="n">
-        <v>63.56</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>166.76</v>
+        <v>502.02</v>
       </c>
       <c r="M8" t="n">
-        <v>32.4</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -972,45 +972,45 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>33955470</v>
+        <v>36334595</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>鑫通源电子</t>
+          <t>付师傅开锁</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>泉州市鑫通源电子科技有限公司</t>
+          <t>厦门市海沧区付师傅锁具维修店</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>429351055</v>
+        <v>429048343</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>首次上线新客户</t>
+          <t>一户多开</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>44496</v>
+        <v>44516</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>45155</v>
+        <v>45190</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>泉州市</t>
+          <t>厦门市</t>
         </is>
       </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.67</v>
+        <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>520.05</v>
       </c>
       <c r="M9" t="n">
         <v>0</v>
@@ -1019,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -1028,7 +1028,7 @@
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1036,63 +1036,63 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>37845140</v>
+        <v>32385679</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>平和华宇</t>
+          <t>泉州海东1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>福建平和华宇机械有限公司</t>
+          <t>泉州海东木制品有限责任公司</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>429427348</v>
+        <v>428452492</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>首次上线新客户</t>
+          <t>一户多开</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>44739</v>
+        <v>44272</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>45154</v>
+        <v>45196</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>漳州市</t>
+          <t>泉州市</t>
         </is>
       </c>
       <c r="J10" t="n">
         <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>4.34</v>
+        <v>13.37</v>
       </c>
       <c r="L10" t="n">
-        <v>6.97</v>
+        <v>1.06</v>
       </c>
       <c r="M10" t="n">
-        <v>1.32</v>
+        <v>14.68</v>
       </c>
       <c r="N10" t="n">
-        <v>5.91</v>
+        <v>31.56</v>
       </c>
       <c r="O10" t="n">
-        <v>8.75</v>
+        <v>23.39</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>12.37</v>
       </c>
       <c r="Q10" t="n">
-        <v>16.92</v>
+        <v>22.76</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>12.75</v>
       </c>
     </row>
     <row r="11">
@@ -1100,66 +1100,4538 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>28055446</v>
+        <v>7310846</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>厦门恳青</t>
+          <t>厦门安政</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>厦门恳青装饰材料有限公司</t>
+          <t>厦门安政交通设施工程有限公司</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>55258157</v>
+        <v>199941619</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>41776</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="L11" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="M11" t="n">
+        <v>536.08</v>
+      </c>
+      <c r="N11" t="n">
+        <v>12.88</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7.65</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>38088606</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>园鑫物流</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>泉州园鑫物流有限公司</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>429425729</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>44603</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>82.73999999999999</v>
+      </c>
+      <c r="L12" t="n">
+        <v>87.61</v>
+      </c>
+      <c r="M12" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="N12" t="n">
+        <v>80.34</v>
+      </c>
+      <c r="O12" t="n">
+        <v>67.81999999999999</v>
+      </c>
+      <c r="P12" t="n">
+        <v>85.18000000000001</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>100.21</v>
+      </c>
+      <c r="R12" t="n">
+        <v>93.01000000000001</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>28758669</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>兆功成驾驶</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>厦门市思明区兆功成驾驶技术咨询服务部</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>429020257</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>43717</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" t="n">
+        <v>217.12</v>
+      </c>
+      <c r="M13" t="n">
+        <v>288.89</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>30500194</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>泉州宜家装饰</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>泉州市宜家装饰工程有限公司</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>57297363</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>老户新开</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>43950</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" t="n">
+        <v>605.64</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>31279864</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>资鑫建筑</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>厦门资鑫建筑工程有限公司</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>429218690</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>44176</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>45189</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>508.46</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>36600723</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>一印百顺</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>厦门一印百顺印章制作有限公司</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>429400664</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>508.26</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>18730491</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>三维云</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>厦门三维云科技有限责任公司</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>428095125</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>42378</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>604.77</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>30628074</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>程溪爱尚</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>龙海市程溪爱尚园艺场</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>429166309</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>43993</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>287.53</v>
+      </c>
+      <c r="M18" t="n">
+        <v>220.15</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>30578956</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>金辉洁回收</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>厦门金辉洁物资回收有限公司</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>428407215</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>老户新开</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>43963</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>252.94</v>
+      </c>
+      <c r="M19" t="n">
+        <v>248.9</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>26910059</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>炎顺建材泉州</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>随州市炎顺建材有限公司泉州分公司</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>428845812</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>43447</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>95.94</v>
+      </c>
+      <c r="L20" t="n">
+        <v>34.91</v>
+      </c>
+      <c r="M20" t="n">
+        <v>290.39</v>
+      </c>
+      <c r="N20" t="n">
+        <v>98.78</v>
+      </c>
+      <c r="O20" t="n">
+        <v>28.52</v>
+      </c>
+      <c r="P20" t="n">
+        <v>32.57</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="R20" t="n">
+        <v>68.7</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>3153991</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>泉州金算盘</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>泉州市金算盘财务咨询有限公司</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>52538745</v>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" s="2" t="n">
+        <v>40730</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>45192</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J21" t="n">
+        <v>1</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>201.65</v>
+      </c>
+      <c r="M21" t="n">
+        <v>203.49</v>
+      </c>
+      <c r="N21" t="n">
+        <v>102.37</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>40025799</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>花仙谷花卉</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>南靖县花仙谷花卉有限公司</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>429465706</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>44679</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>502.13</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>40973819</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>宣羽田</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>厦门宣羽田网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>429493239</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>44739</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J23" t="n">
+        <v>1</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" t="n">
+        <v>501.12</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>40183088</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>红创家具</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>晋江市池店镇红创家具商行</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>429469628</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>44682</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>45192</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J24" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" t="n">
+        <v>266.06</v>
+      </c>
+      <c r="N24" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>30731403</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>xm三普</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>厦门市三普科技有限公司</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>428575879</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
           <t>一户多开</t>
         </is>
       </c>
-      <c r="G11" s="2" t="n">
-        <v>43720</v>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>45155</v>
-      </c>
-      <c r="I11" t="inlineStr">
+      <c r="G25" s="2" t="n">
+        <v>43990</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>45189</v>
+      </c>
+      <c r="I25" t="inlineStr">
         <is>
           <t>厦门市</t>
         </is>
       </c>
-      <c r="J11" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" t="n">
-        <v>16.77</v>
-      </c>
-      <c r="L11" t="n">
-        <v>93.40000000000001</v>
-      </c>
-      <c r="M11" t="n">
-        <v>48.04</v>
-      </c>
-      <c r="N11" t="n">
-        <v>33.23</v>
-      </c>
-      <c r="O11" t="n">
-        <v>79.29000000000001</v>
-      </c>
-      <c r="P11" t="n">
-        <v>31.07</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>42.48</v>
-      </c>
-      <c r="R11" t="n">
-        <v>41.57</v>
+      <c r="J25" t="n">
+        <v>1</v>
+      </c>
+      <c r="K25" t="n">
+        <v>434.83</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>28309818</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>鼎创希</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>厦门鼎创希文化传媒有限公司</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>428991613</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>43668</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K26" t="n">
+        <v>400.03</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>56.95</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>33132479</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>鹿原物流</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>晋江市陈埭镇鹿原货物代理服务部</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>429318573</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>44363</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>45194</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J27" t="n">
+        <v>1</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" t="n">
+        <v>116.5</v>
+      </c>
+      <c r="M27" t="n">
+        <v>208.86</v>
+      </c>
+      <c r="N27" t="n">
+        <v>101.11</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>27752821</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>亨骏名匠</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>亨骏名匠钟表维修（厦门）有限公司</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>428943947</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>43577</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>45192</v>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J28" t="n">
+        <v>1</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>502.08</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>22839498</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>锐诚防水</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>泉州锐诚建筑防水工程有限公司</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>428457562</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>42728</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J29" t="n">
+        <v>1</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" t="n">
+        <v>243.94</v>
+      </c>
+      <c r="M29" t="n">
+        <v>262.39</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>32894649</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>颜艺彬园艺</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>高新区九湖颜艺彬园艺场</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>429308861</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>44326</v>
+      </c>
+      <c r="H30" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J30" t="n">
+        <v>1</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" t="n">
+        <v>108.08</v>
+      </c>
+      <c r="M30" t="n">
+        <v>397.6</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>26463585</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>璐霖回收</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>南安市丰州璐霖废品回收站</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>428843680</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>43372</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J31" t="n">
+        <v>1</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" t="n">
+        <v>36.21</v>
+      </c>
+      <c r="N31" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="O31" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="P31" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>102.92</v>
+      </c>
+      <c r="R31" t="n">
+        <v>105.46</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>34064627</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>欧科衡器1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>福建欧科衡器有限公司</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>429206596</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>44406</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>45193</v>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J32" t="n">
+        <v>1</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" t="n">
+        <v>246.47</v>
+      </c>
+      <c r="N32" t="n">
+        <v>192.72</v>
+      </c>
+      <c r="O32" t="n">
+        <v>82.43000000000001</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>27090410</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>尊享会</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>厦门尊享会汽车服务有限公司</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>428888248</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>43559</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>514.24</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>34193150</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>万红农业</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>漳州万红农业发展有限公司</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>429359252</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>44425</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J34" t="n">
+        <v>1</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" t="n">
+        <v>503.1</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>2958522</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>新果苗场</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>平和县山新果苗场</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>52174907</v>
+      </c>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" s="2" t="n">
+        <v>40691</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J35" t="n">
+        <v>1</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" t="n">
+        <v>503.52</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>30523289</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>金饰红陶瓷</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>晋江金饰红陶瓷有限公司</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>429157310</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>44260</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J36" t="n">
+        <v>1</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" t="n">
+        <v>496.41</v>
+      </c>
+      <c r="M36" t="n">
+        <v>20.95</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>33918138</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>进发沙发翻新</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>丰泽区进发沙发翻新店</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>428560206</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>老户新开</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>44410</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>45193</v>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J37" t="n">
+        <v>1</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" t="n">
+        <v>21.04</v>
+      </c>
+      <c r="M37" t="n">
+        <v>152.92</v>
+      </c>
+      <c r="N37" t="n">
+        <v>225.91</v>
+      </c>
+      <c r="O37" t="n">
+        <v>146.01</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36530020</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>瑞爱妮</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>漳州市芗城区瑞爱妮假发店</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>429399160</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>44531</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J38" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" t="n">
+        <v>507.43</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>31061902</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>厦门人人装</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>人人装（厦门）网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>429205107</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>44067</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J39" t="n">
+        <v>1</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" t="n">
+        <v>512.4</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>8184410</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>育红蜜柚</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>福建省平和县育红蜜柚种苗有限公司</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>200254696</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>42013</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J40" t="n">
+        <v>1</v>
+      </c>
+      <c r="K40" t="n">
+        <v>83.44</v>
+      </c>
+      <c r="L40" t="n">
+        <v>436.46</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" t="n">
+        <v>36732943</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>厦门三略</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>厦门三略管理顾问有限公司</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>429403822</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>44544</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J41" t="n">
+        <v>1</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" t="n">
+        <v>151.6</v>
+      </c>
+      <c r="M41" t="n">
+        <v>353.25</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" t="n">
+        <v>28415983</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>厦门木之森</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>厦门木之森香文化传播有限公司</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>428993569</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>43655</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>45194</v>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J42" t="n">
+        <v>1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>51.62</v>
+      </c>
+      <c r="L42" t="n">
+        <v>35.92</v>
+      </c>
+      <c r="M42" t="n">
+        <v>37.05</v>
+      </c>
+      <c r="N42" t="n">
+        <v>39.78</v>
+      </c>
+      <c r="O42" t="n">
+        <v>23.71</v>
+      </c>
+      <c r="P42" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" t="n">
+        <v>24038236</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>厦门瑞彼德</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>厦门瑞彼德网络工程有限公司</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>428516729</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>42914</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J43" t="n">
+        <v>1</v>
+      </c>
+      <c r="K43" t="n">
+        <v>496.17</v>
+      </c>
+      <c r="L43" t="n">
+        <v>38.92</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" t="n">
+        <v>37032990</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>瑞派卡比</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>漳州市龙文区瑞派卡比宠物医院有限公司</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>429409475</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>44541</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J44" t="n">
+        <v>1</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" t="n">
+        <v>507.88</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" t="n">
+        <v>31327773</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>戎丰01</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>厦门戎丰电气设备有限公司</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>429222020</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>44175</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J45" t="n">
+        <v>1</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
+        <v>450.27</v>
+      </c>
+      <c r="M45" t="n">
+        <v>93.92</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" t="n">
+        <v>26922223</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>漳州鸿景</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>漳州鸿景园林绿化工程有限公司</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>428877231</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>43480</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J46" t="n">
+        <v>1</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" t="n">
+        <v>511.94</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" t="n">
+        <v>37845140</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>平和华宇</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>福建平和华宇机械有限公司</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>429427348</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>44739</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J47" t="n">
+        <v>1</v>
+      </c>
+      <c r="K47" t="n">
+        <v>4.46</v>
+      </c>
+      <c r="L47" t="n">
+        <v>281.59</v>
+      </c>
+      <c r="M47" t="n">
+        <v>17.66</v>
+      </c>
+      <c r="N47" t="n">
+        <v>29.08</v>
+      </c>
+      <c r="O47" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="P47" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" t="n">
+        <v>29867833</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>李永康琴行</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>漳州市芗城区李永康琴行</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>429125979</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>43981</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J48" t="n">
+        <v>1</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" t="n">
+        <v>525.4299999999999</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" t="n">
+        <v>33955470</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>鑫通源电子</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>泉州市鑫通源电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>429351055</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>44496</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>1</v>
+      </c>
+      <c r="K49" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="L49" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="M49" t="n">
+        <v>29.74</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="P49" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>23.93</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" t="n">
+        <v>26714943</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>pinzhuan-中国利郎</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>利郎（中国）有限公司</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>60887991</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>43419</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>1</v>
+      </c>
+      <c r="K50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="L50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="M50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="N50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="O50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="P50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>2523.99</v>
+      </c>
+      <c r="R50" t="n">
+        <v>2523.99</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" t="n">
+        <v>33056204</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>珑琨陶瓷</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>福建珑琨陶瓷发展集团有限公司</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>429315266</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>44358</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>45195</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>1</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>501.31</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" t="n">
+        <v>30547577</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>德融万通</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>厦门市德融万通网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>429159702</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>44375</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>45189</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>1</v>
+      </c>
+      <c r="K52" t="n">
+        <v>505.53</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" t="n">
+        <v>32612652</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>xm雨果网</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>雨果跨境（厦门）科技有限公司</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>429146804</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>44305</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>1</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" t="n">
+        <v>148.57</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" t="n">
+        <v>40181852</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>漳州欧凯</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>漳州欧凯家具有限公司</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>429469580</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>44739</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>1</v>
+      </c>
+      <c r="K54" t="n">
+        <v>496.19</v>
+      </c>
+      <c r="L54" t="n">
+        <v>58.36</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" t="n">
+        <v>38156639</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>彼之良</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>漳州彼之良网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>429426735</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>44648</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>1</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" t="n">
+        <v>500.34</v>
+      </c>
+      <c r="M55" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" t="n">
+        <v>32622428</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>福建诚胜隆</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>福建省诚胜隆工贸有限公司</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>429296551</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>44299</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>1</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" t="n">
+        <v>504.2</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" t="n">
+        <v>32636221</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>朗国清关</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>朗国清关（厦门）信息服务有限公司</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>429297320</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>首次上线新客户</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>44299</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>1</v>
+      </c>
+      <c r="K57" t="n">
+        <v>200.05</v>
+      </c>
+      <c r="L57" t="n">
+        <v>301.48</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" t="n">
+        <v>50253139</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>厦门易成功</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>易成功（厦门）信息科技有限公司</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>429452368</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>45188</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>1</v>
+      </c>
+      <c r="K58" t="n">
+        <v>302.89</v>
+      </c>
+      <c r="L58" t="n">
+        <v>301.61</v>
+      </c>
+      <c r="M58" t="n">
+        <v>326.04</v>
+      </c>
+      <c r="N58" t="n">
+        <v>306.26</v>
+      </c>
+      <c r="O58" t="n">
+        <v>300.75</v>
+      </c>
+      <c r="P58" t="n">
+        <v>312.97</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>305.14</v>
+      </c>
+      <c r="R58" t="n">
+        <v>306.68</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" t="n">
+        <v>49490076</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>吴东升美容4</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>45146</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>1</v>
+      </c>
+      <c r="K59" t="n">
+        <v>854.76</v>
+      </c>
+      <c r="L59" t="n">
+        <v>1140.87</v>
+      </c>
+      <c r="M59" t="n">
+        <v>1781.06</v>
+      </c>
+      <c r="N59" t="n">
+        <v>1089.2</v>
+      </c>
+      <c r="O59" t="n">
+        <v>1145.35</v>
+      </c>
+      <c r="P59" t="n">
+        <v>974.62</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>1658.88</v>
+      </c>
+      <c r="R59" t="n">
+        <v>936.12</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" t="n">
+        <v>50037427</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>吴东升美容15</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>45180</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>1</v>
+      </c>
+      <c r="K60" t="n">
+        <v>349.47</v>
+      </c>
+      <c r="L60" t="n">
+        <v>86.53</v>
+      </c>
+      <c r="M60" t="n">
+        <v>233.63</v>
+      </c>
+      <c r="N60" t="n">
+        <v>426.3</v>
+      </c>
+      <c r="O60" t="n">
+        <v>279.06</v>
+      </c>
+      <c r="P60" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>400.96</v>
+      </c>
+      <c r="R60" t="n">
+        <v>379.37</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" t="n">
+        <v>49543849</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>静帮2</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>厦门静帮信息技术有限公司</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>429677016</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>45141</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>1</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" t="n">
+        <v>49481807</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>厦门郝诚钢结构</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>厦门郝诚钢结构有限公司</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>428558219</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>45135</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>1</v>
+      </c>
+      <c r="K62" t="n">
+        <v>157.23</v>
+      </c>
+      <c r="L62" t="n">
+        <v>157.99</v>
+      </c>
+      <c r="M62" t="n">
+        <v>123.96</v>
+      </c>
+      <c r="N62" t="n">
+        <v>167.27</v>
+      </c>
+      <c r="O62" t="n">
+        <v>124.97</v>
+      </c>
+      <c r="P62" t="n">
+        <v>200.35</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>153.8</v>
+      </c>
+      <c r="R62" t="n">
+        <v>183.21</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" t="n">
+        <v>50382029</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>xm佰名</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>厦门佰名网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>429679173</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>45188</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>1</v>
+      </c>
+      <c r="K63" t="n">
+        <v>333.52</v>
+      </c>
+      <c r="L63" t="n">
+        <v>356.35</v>
+      </c>
+      <c r="M63" t="n">
+        <v>259.34</v>
+      </c>
+      <c r="N63" t="n">
+        <v>122.75</v>
+      </c>
+      <c r="O63" t="n">
+        <v>130.21</v>
+      </c>
+      <c r="P63" t="n">
+        <v>246.74</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>501.51</v>
+      </c>
+      <c r="R63" t="n">
+        <v>445.58</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" t="n">
+        <v>50075515</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>医肤堂2</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>漳州医肤堂医疗投资有限公司</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>429690845</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>45174</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>1</v>
+      </c>
+      <c r="K64" t="n">
+        <v>79.87</v>
+      </c>
+      <c r="L64" t="n">
+        <v>70.44</v>
+      </c>
+      <c r="M64" t="n">
+        <v>119.76</v>
+      </c>
+      <c r="N64" t="n">
+        <v>85.42</v>
+      </c>
+      <c r="O64" t="n">
+        <v>100.52</v>
+      </c>
+      <c r="P64" t="n">
+        <v>302.85</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>216.84</v>
+      </c>
+      <c r="R64" t="n">
+        <v>176.48</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" t="n">
+        <v>49490185</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>吴东升美容6</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>45157</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>1</v>
+      </c>
+      <c r="K65" t="n">
+        <v>694.59</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1124.3</v>
+      </c>
+      <c r="M65" t="n">
+        <v>596.96</v>
+      </c>
+      <c r="N65" t="n">
+        <v>923.91</v>
+      </c>
+      <c r="O65" t="n">
+        <v>549.67</v>
+      </c>
+      <c r="P65" t="n">
+        <v>514.59</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>667.8099999999999</v>
+      </c>
+      <c r="R65" t="n">
+        <v>1253.58</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" t="n">
+        <v>49731362</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>康辉西林1</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>厦门康辉国际旅行社有限公司西林东路门市部</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>429681851</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>45169</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" t="n">
+        <v>29.26</v>
+      </c>
+      <c r="L66" t="n">
+        <v>23.24</v>
+      </c>
+      <c r="M66" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="N66" t="n">
+        <v>29.72</v>
+      </c>
+      <c r="O66" t="n">
+        <v>33.47</v>
+      </c>
+      <c r="P66" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>14.62</v>
+      </c>
+      <c r="R66" t="n">
+        <v>19.62</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" t="n">
+        <v>49490289</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>吴东升美容8</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>45163</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>1</v>
+      </c>
+      <c r="K67" t="n">
+        <v>3183.82</v>
+      </c>
+      <c r="L67" t="n">
+        <v>2550.95</v>
+      </c>
+      <c r="M67" t="n">
+        <v>1555.69</v>
+      </c>
+      <c r="N67" t="n">
+        <v>1756.15</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1698.5</v>
+      </c>
+      <c r="P67" t="n">
+        <v>1363.63</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1565.02</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1798.48</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" t="n">
+        <v>50037323</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>吴东升美容13</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>45186</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>1</v>
+      </c>
+      <c r="K68" t="n">
+        <v>2725.53</v>
+      </c>
+      <c r="L68" t="n">
+        <v>1848.27</v>
+      </c>
+      <c r="M68" t="n">
+        <v>2603.91</v>
+      </c>
+      <c r="N68" t="n">
+        <v>2711.47</v>
+      </c>
+      <c r="O68" t="n">
+        <v>3465.65</v>
+      </c>
+      <c r="P68" t="n">
+        <v>2891.02</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>3586.3</v>
+      </c>
+      <c r="R68" t="n">
+        <v>3813.16</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" t="n">
+        <v>49152779</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>厦门利成</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>厦门利成智能科技有限公司</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>429270959</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>45126</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>1</v>
+      </c>
+      <c r="K69" t="n">
+        <v>26.4</v>
+      </c>
+      <c r="L69" t="n">
+        <v>17.28</v>
+      </c>
+      <c r="M69" t="n">
+        <v>13.63</v>
+      </c>
+      <c r="N69" t="n">
+        <v>24.22</v>
+      </c>
+      <c r="O69" t="n">
+        <v>36.7</v>
+      </c>
+      <c r="P69" t="n">
+        <v>22.58</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>19.54</v>
+      </c>
+      <c r="R69" t="n">
+        <v>23.79</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" t="n">
+        <v>50514859</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>xm小荷尖尖</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>厦门小荷尖尖网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>429055075</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>45191</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>1</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" t="n">
+        <v>510.58</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" t="n">
+        <v>50075558</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>医肤堂3</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>漳州医肤堂医疗投资有限公司</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>429690845</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>45183</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>漳州市</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>1</v>
+      </c>
+      <c r="K71" t="n">
+        <v>129.39</v>
+      </c>
+      <c r="L71" t="n">
+        <v>158.48</v>
+      </c>
+      <c r="M71" t="n">
+        <v>132.49</v>
+      </c>
+      <c r="N71" t="n">
+        <v>43.02</v>
+      </c>
+      <c r="O71" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="P71" t="n">
+        <v>15.53</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>40.23</v>
+      </c>
+      <c r="R71" t="n">
+        <v>8.25</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>70</v>
+      </c>
+      <c r="B72" t="n">
+        <v>50504499</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>珂芙汝1</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>厦门珂芙汝文化传媒有限公司</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>429666785</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>45190</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>1</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" t="n">
+        <v>62.84</v>
+      </c>
+      <c r="M72" t="n">
+        <v>1301.79</v>
+      </c>
+      <c r="N72" t="n">
+        <v>1069.77</v>
+      </c>
+      <c r="O72" t="n">
+        <v>1696.53</v>
+      </c>
+      <c r="P72" t="n">
+        <v>1166.64</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>1465.59</v>
+      </c>
+      <c r="R72" t="n">
+        <v>1331.07</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>71</v>
+      </c>
+      <c r="B73" t="n">
+        <v>49742518</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>泉州益森能1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>泉州益森能液压机电设备有限公司</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>429306033</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>45175</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>1</v>
+      </c>
+      <c r="K73" t="n">
+        <v>106.14</v>
+      </c>
+      <c r="L73" t="n">
+        <v>56.49</v>
+      </c>
+      <c r="M73" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="N73" t="n">
+        <v>77.31</v>
+      </c>
+      <c r="O73" t="n">
+        <v>131.77</v>
+      </c>
+      <c r="P73" t="n">
+        <v>14.05</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>58.11</v>
+      </c>
+      <c r="R73" t="n">
+        <v>118.68</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>72</v>
+      </c>
+      <c r="B74" t="n">
+        <v>50119236</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>吴东升美容16</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>45174</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>1</v>
+      </c>
+      <c r="K74" t="n">
+        <v>906.78</v>
+      </c>
+      <c r="L74" t="n">
+        <v>889.41</v>
+      </c>
+      <c r="M74" t="n">
+        <v>874.17</v>
+      </c>
+      <c r="N74" t="n">
+        <v>1284.78</v>
+      </c>
+      <c r="O74" t="n">
+        <v>926.89</v>
+      </c>
+      <c r="P74" t="n">
+        <v>1017.64</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>642.03</v>
+      </c>
+      <c r="R74" t="n">
+        <v>423.91</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" t="n">
+        <v>50037393</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>吴东升美容14</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>45182</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1988.9</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2547.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1714.89</v>
+      </c>
+      <c r="N75" t="n">
+        <v>3172.52</v>
+      </c>
+      <c r="O75" t="n">
+        <v>2504.23</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2322.7</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>2576.62</v>
+      </c>
+      <c r="R75" t="n">
+        <v>3153.67</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" t="n">
+        <v>49449610</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>吴东升美容1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>45140</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>1</v>
+      </c>
+      <c r="K76" t="n">
+        <v>5659.48</v>
+      </c>
+      <c r="L76" t="n">
+        <v>4962.97</v>
+      </c>
+      <c r="M76" t="n">
+        <v>4596.65</v>
+      </c>
+      <c r="N76" t="n">
+        <v>5492.5</v>
+      </c>
+      <c r="O76" t="n">
+        <v>6067.26</v>
+      </c>
+      <c r="P76" t="n">
+        <v>3909.4</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>4525.43</v>
+      </c>
+      <c r="R76" t="n">
+        <v>4149.9</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" t="n">
+        <v>49490317</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>吴东升美容9</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>45153</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>1</v>
+      </c>
+      <c r="K77" t="n">
+        <v>129.86</v>
+      </c>
+      <c r="L77" t="n">
+        <v>326.09</v>
+      </c>
+      <c r="M77" t="n">
+        <v>184.24</v>
+      </c>
+      <c r="N77" t="n">
+        <v>160.25</v>
+      </c>
+      <c r="O77" t="n">
+        <v>170.5</v>
+      </c>
+      <c r="P77" t="n">
+        <v>51.63</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>9.49</v>
+      </c>
+      <c r="R77" t="n">
+        <v>113.55</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" t="n">
+        <v>48831487</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>邦唱网络科技</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>厦门邦唱网络科技有限公司</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>428788943</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>45119</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>厦门市</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>1</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="L78" t="n">
+        <v>18.1</v>
+      </c>
+      <c r="M78" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="N78" t="n">
+        <v>11.91</v>
+      </c>
+      <c r="O78" t="n">
+        <v>18.37</v>
+      </c>
+      <c r="P78" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="R78" t="n">
+        <v>10.66</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" t="n">
+        <v>49069396</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>阿波罗检测</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>泉州市阿波罗质量检测服务有限公司</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>429000745</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>45127</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>45194</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>1</v>
+      </c>
+      <c r="K79" t="n">
+        <v>52.83</v>
+      </c>
+      <c r="L79" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="M79" t="n">
+        <v>56.53</v>
+      </c>
+      <c r="N79" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="O79" t="n">
+        <v>52.74</v>
+      </c>
+      <c r="P79" t="n">
+        <v>25.01</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" t="n">
+        <v>49490133</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>吴东升美容5</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>45145</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" t="n">
+        <v>1396.13</v>
+      </c>
+      <c r="L80" t="n">
+        <v>931.59</v>
+      </c>
+      <c r="M80" t="n">
+        <v>2300.28</v>
+      </c>
+      <c r="N80" t="n">
+        <v>2863.63</v>
+      </c>
+      <c r="O80" t="n">
+        <v>1877.8</v>
+      </c>
+      <c r="P80" t="n">
+        <v>2096.71</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>1442.5</v>
+      </c>
+      <c r="R80" t="n">
+        <v>1547.76</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" t="n">
+        <v>49490343</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>吴东升美容10</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>丰泽区泉秀吴东升美容服务店</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>429674636</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>一户多开</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>45164</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>45196</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>泉州市</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>1</v>
+      </c>
+      <c r="K81" t="n">
+        <v>10148.12</v>
+      </c>
+      <c r="L81" t="n">
+        <v>6191.98</v>
+      </c>
+      <c r="M81" t="n">
+        <v>6496.23</v>
+      </c>
+      <c r="N81" t="n">
+        <v>8315.290000000001</v>
+      </c>
+      <c r="O81" t="n">
+        <v>9548.620000000001</v>
+      </c>
+      <c r="P81" t="n">
+        <v>7263.02</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>8852.17</v>
+      </c>
+      <c r="R81" t="n">
+        <v>10052.25</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>